--- a/data/trans_orig/P36BPD02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023</t>
+          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023 (tasa de respuesta: 96,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54413</t>
+          <t>55057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85332</t>
+          <t>85998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85880</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115208</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150224</t>
+          <t>148621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191303</t>
+          <t>191358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249158</t>
+          <t>249664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298865</t>
+          <t>300361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260538</t>
+          <t>257940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301159</t>
+          <t>297983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>520112</t>
+          <t>522691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579767</t>
+          <t>586432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219324</t>
+          <t>220234</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>270497</t>
+          <t>269657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>243177</t>
+          <t>242103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>283846</t>
+          <t>280729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>478581</t>
+          <t>473952</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>542155</t>
+          <t>539978</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>71645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216679</t>
+          <t>216246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121894</t>
+          <t>122338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160223</t>
+          <t>161775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>177171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349810</t>
+          <t>353245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217824</t>
+          <t>208795</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>537646</t>
+          <t>534152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422638</t>
+          <t>419915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>470692</t>
+          <t>470260</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>484009</t>
+          <t>560260</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>988796</t>
+          <t>989325</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>392493</t>
+          <t>395207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>838571</t>
+          <t>846606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>291226</t>
+          <t>288717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>337740</t>
+          <t>339829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>709375</t>
+          <t>708258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1390332</t>
+          <t>1321352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74793</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117222</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>48576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>154107</t>
+          <t>153230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134782</t>
+          <t>125216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>248906</t>
+          <t>250166</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294433</t>
+          <t>295658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356882</t>
+          <t>352410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181992</t>
+          <t>153664</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456116</t>
+          <t>452128</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429865</t>
+          <t>425557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>783708</t>
+          <t>786158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205458</t>
+          <t>207511</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264071</t>
+          <t>261004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296649</t>
+          <t>304274</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644672</t>
+          <t>693267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529077</t>
+          <t>527685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>983658</t>
+          <t>1000685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98959</t>
+          <t>99717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143908</t>
+          <t>142640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110829</t>
+          <t>110254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163629</t>
+          <t>164432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224907</t>
+          <t>226045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291403</t>
+          <t>293693</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375349</t>
+          <t>376213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439379</t>
+          <t>438483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>368321</t>
+          <t>378810</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>506000</t>
+          <t>508234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>773920</t>
+          <t>767733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>926601</t>
+          <t>926285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>353427</t>
+          <t>356146</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>419929</t>
+          <t>418557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>430078</t>
+          <t>431142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>593764</t>
+          <t>600596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>808249</t>
+          <t>807366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1003921</t>
+          <t>1002870</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340315</t>
+          <t>331562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>500955</t>
+          <t>496845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>402364</t>
+          <t>396161</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>544077</t>
+          <t>549400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>812749</t>
+          <t>796082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1010541</t>
+          <t>1017847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1092043</t>
+          <t>1059384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1552674</t>
+          <t>1546941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1255156</t>
+          <t>1207835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1662853</t>
+          <t>1667796</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2547836</t>
+          <t>2531860</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3162104</t>
+          <t>3151034</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1253722</t>
+          <t>1260347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1846244</t>
+          <t>1879156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1336762</t>
+          <t>1329386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1880700</t>
+          <t>1927753</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2661458</t>
+          <t>2666294</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3471391</t>
+          <t>3458948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>77916</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55057</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>96197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100149</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85723</t>
+          <t>96321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>129195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>168653</t>
+          <t>188916</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148621</t>
+          <t>167311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191358</t>
+          <t>213532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>273688</t>
+          <t>297468</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249664</t>
+          <t>270720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>323233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278487</t>
+          <t>304905</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257940</t>
+          <t>279365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297983</t>
+          <t>324805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>552174</t>
+          <t>602372</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522691</t>
+          <t>567958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586432</t>
+          <t>634997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>245184</t>
+          <t>261572</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220234</t>
+          <t>235951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269657</t>
+          <t>286845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>262608</t>
+          <t>277219</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242103</t>
+          <t>256391</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>280729</t>
+          <t>301049</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>507792</t>
+          <t>538790</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>473952</t>
+          <t>509662</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>539978</t>
+          <t>574628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>587375</t>
+          <t>636956</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>587375</t>
+          <t>636956</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>587375</t>
+          <t>636956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>641244</t>
+          <t>693123</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>641244</t>
+          <t>693123</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>641244</t>
+          <t>693123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1228619</t>
+          <t>1330078</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1228619</t>
+          <t>1330078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1228619</t>
+          <t>1330078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>158525</t>
+          <t>193312</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71645</t>
+          <t>168353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216246</t>
+          <t>230110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>156826</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122338</t>
+          <t>137260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161775</t>
+          <t>181141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>299012</t>
+          <t>350138</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177171</t>
+          <t>315710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353245</t>
+          <t>387943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>409653</t>
+          <t>449060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>208795</t>
+          <t>415940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>534152</t>
+          <t>485346</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>446504</t>
+          <t>505044</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>419915</t>
+          <t>473385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>470260</t>
+          <t>531223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>856156</t>
+          <t>954104</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>560260</t>
+          <t>913492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>989325</t>
+          <t>1003733</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>565898</t>
+          <t>343677</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>395207</t>
+          <t>310225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>846606</t>
+          <t>374414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>315405</t>
+          <t>350590</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>288717</t>
+          <t>324733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339829</t>
+          <t>380293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>881303</t>
+          <t>694267</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>708258</t>
+          <t>649200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1321352</t>
+          <t>734966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1134076</t>
+          <t>986049</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1134076</t>
+          <t>986049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1134076</t>
+          <t>986049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>902396</t>
+          <t>1012460</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>902396</t>
+          <t>1012460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>902396</t>
+          <t>1012460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2036472</t>
+          <t>1998509</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2036472</t>
+          <t>1998509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2036472</t>
+          <t>1998509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94922</t>
+          <t>114968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>95396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117622</t>
+          <t>138926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>139334</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48576</t>
+          <t>120325</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153230</t>
+          <t>161786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>207047</t>
+          <t>254302</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125216</t>
+          <t>223282</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250166</t>
+          <t>285399</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>324645</t>
+          <t>362528</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>295658</t>
+          <t>331805</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>352410</t>
+          <t>394259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>340789</t>
+          <t>357501</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153664</t>
+          <t>330306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>452128</t>
+          <t>383525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>665435</t>
+          <t>720029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>425557</t>
+          <t>679339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>786158</t>
+          <t>759026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>231947</t>
+          <t>262253</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207511</t>
+          <t>233747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261004</t>
+          <t>293779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>444418</t>
+          <t>274037</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>304274</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>693267</t>
+          <t>298255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>676365</t>
+          <t>536290</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>527685</t>
+          <t>500020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1000685</t>
+          <t>576230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>651514</t>
+          <t>739749</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>651514</t>
+          <t>739749</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>651514</t>
+          <t>739749</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>897333</t>
+          <t>770872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>897333</t>
+          <t>770872</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>897333</t>
+          <t>770872</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1548847</t>
+          <t>1510621</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1548847</t>
+          <t>1510621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1548847</t>
+          <t>1510621</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>141752</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99717</t>
+          <t>116089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142640</t>
+          <t>164732</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139732</t>
+          <t>167536</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110254</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164432</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>258979</t>
+          <t>309287</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226045</t>
+          <t>277322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>293693</t>
+          <t>344060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>406439</t>
+          <t>437755</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>376213</t>
+          <t>405422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438483</t>
+          <t>472721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>465458</t>
+          <t>511030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>378810</t>
+          <t>483386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>508234</t>
+          <t>542514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>871897</t>
+          <t>948785</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>767733</t>
+          <t>904235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>926285</t>
+          <t>996186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>385958</t>
+          <t>395507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>356146</t>
+          <t>361741</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>418557</t>
+          <t>428543</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>480673</t>
+          <t>430867</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>431142</t>
+          <t>400458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>600596</t>
+          <t>457490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>866632</t>
+          <t>826374</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>807366</t>
+          <t>783926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1002870</t>
+          <t>870016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>911644</t>
+          <t>975014</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>911644</t>
+          <t>975014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>911644</t>
+          <t>975014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1085863</t>
+          <t>1109432</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1085863</t>
+          <t>1109432</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1085863</t>
+          <t>1109432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1997507</t>
+          <t>2084446</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1997507</t>
+          <t>2084446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1997507</t>
+          <t>2084446</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>441198</t>
+          <t>527947</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331562</t>
+          <t>480993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>496845</t>
+          <t>572113</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>492494</t>
+          <t>574695</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>396161</t>
+          <t>534038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>549400</t>
+          <t>612870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>933691</t>
+          <t>1102642</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796082</t>
+          <t>1044692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1017847</t>
+          <t>1158614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1414425</t>
+          <t>1546811</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1059384</t>
+          <t>1483131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1546941</t>
+          <t>1612345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1531237</t>
+          <t>1678480</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1207835</t>
+          <t>1625840</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1667796</t>
+          <t>1734171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2945662</t>
+          <t>3225291</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2531860</t>
+          <t>3142902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3151034</t>
+          <t>3306702</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1428987</t>
+          <t>1263009</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1260347</t>
+          <t>1195506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1879156</t>
+          <t>1324237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1503105</t>
+          <t>1332713</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1329386</t>
+          <t>1273930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1927753</t>
+          <t>1380520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2932092</t>
+          <t>2595722</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2666294</t>
+          <t>2515535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3458948</t>
+          <t>2678539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>38,69%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3284609</t>
+          <t>3337768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3526836</t>
+          <t>3585888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6811445</t>
+          <t>6923655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
